--- a/db/questionDetails.xlsx
+++ b/db/questionDetails.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,21 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>guest@test.com</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1776449481385</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{'1': {'question': 'Given a binary tree where each node has a value and a list of children, write a function to check if the tree is a valid binary search tree.', 'difficultyLevel': 'easy', 'examples': {'1': {'input': '{1, {2, {3, null, null}, {4, null, null}}, {5, {6, null, null}, {7, null, null}}}', 'output': 'true', 'explanation': 'This is a valid binary search tree because all values in the left subtree are less than the root and all values in the right subtree are greater than the root.'}}, 'constraints': {'1': 'The tree is not empty', '2': 'The tree is a binary tree'}}, '2': {'question': 'Write a function to find the maximum depth of a binary tree.', 'difficultyLevel': 'easy', 'examples': {'1': {'input': '{1, {2, null, null}, {3, {4, null, null}, {5, null, null}}}', 'output': '3', 'explanation': 'The maximum depth of this tree is 3 because the longest path from the root to a leaf is 1 -&gt; 2 -&gt; 3'}}, 'constraints': {'1': 'The tree is not empty', '2': 'The tree is a binary tree'}}, '3': {'question': 'Given a tree where each node has a value and a list of children, write a function to find the path from the root to a given node.', 'difficultyLevel': 'easy', 'examples': {'1': {'input': '{1, {2, {3, null, null}, {4, null, null}}, {5, {6, null, null}, {7, null, null}}}, 3', 'output': '[1, 2, 3]', 'explanation': 'This is the path from the root to the node with value 3'}}, 'constraints': {'1': 'The tree is not empty', '2': 'The tree is a binary tree'}}, '4': {'question': 'Write a function to check if a tree is a perfect binary tree.', 'difficultyLevel': 'easy', 'examples': {'1': {'input': '{1, {2, {3, null, null}, {4, null, null}}, {5, {6, null, null}, {7, null, null}}}', 'output': 'false', 'explanation': 'This is not a perfect binary tree because some nodes have more than two children'}}, 'constraints': {'1': 'The tree is not empty', '2': 'The tree is a binary tree'}}, '5': {'question': 'Given a tree where each node has a value and a list of children, write a function to find the height of the tree.', 'difficultyLevel': 'easy', 'examples': {'1': {'input': '{1, {2, {3, null, null}, {4, null, null}}, {5, {6, null, null}, {7, null, null}}}', 'output': '2', 'explanation': 'The height of this tree is 2 because the longest path from the root to a leaf is 1 -&gt; 2'}}, 'constraints': {'1': 'The tree is not empty', '2': 'The tree is a binary tree'}}}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
